--- a/视频/70篇重点词汇.xlsx
+++ b/视频/70篇重点词汇.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="70篇重点词汇" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="70篇重点词汇" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EJ57"/>
+  <dimension ref="A1:EJ61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1662,12 +1662,12 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>raided</t>
+          <t>accomplice</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>抢劫</t>
+          <t>同伙</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -2364,12 +2364,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>in broad daylight</t>
+          <t>raided</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>光天化日之下</t>
+          <t>抢劫了</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -3066,12 +3066,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>disguise</t>
+          <t>in broad daylight</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>伪装</t>
+          <t>光天化日之下</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -3768,12 +3768,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>camouflage</t>
+          <t>disguise</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>伪装</t>
+          <t>乔装</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -4470,12 +4470,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>rubbed on</t>
+          <t>camouflage</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>涂抹</t>
+          <t>伪装</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -5172,12 +5172,12 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>earnest</t>
+          <t>rubbed on</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>真心实意的</t>
+          <t>涂抹</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -5874,12 +5874,12 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>conviction</t>
+          <t>earnest</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>信念</t>
+          <t>真心实意的</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -6576,12 +6576,12 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>render</t>
+          <t>conviction</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>使变得</t>
+          <t>信念</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>赢得</t>
+          <t>挣得</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -7278,12 +7278,12 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>rationale</t>
+          <t>render</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>理由</t>
+          <t>使</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -7980,22 +7980,22 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>a kernel of truth</t>
+          <t>rationale</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>几分道理</t>
+          <t>逻辑</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>surrender</t>
+          <t>instantly</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>屈服</t>
+          <t>立刻</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -8682,22 +8682,22 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>time-honoured</t>
+          <t>kernel</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>历史悠久的</t>
+          <t>内核</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>instantly</t>
+          <t>surrender</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>立刻</t>
+          <t>缴械投降</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -9384,12 +9384,12 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>inventive</t>
+          <t>time-honoured</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>富有创意的</t>
+          <t>由来已久的</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -10086,22 +10086,22 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>leap</t>
+          <t>ink</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>飞跃</t>
+          <t>墨水</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Follow-ups</t>
+          <t>hold out</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>后续研究</t>
+          <t>坚持抵抗，拒不妥协</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -10788,22 +10788,22 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>self-portrait</t>
+          <t>inventive</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>自拍照</t>
+          <t>富有创意的</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>legendary</t>
+          <t>Follow-ups</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>传奇的</t>
+          <t>后续研究</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -11490,22 +11490,22 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>devoid of</t>
+          <t>leap</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>没有，缺乏</t>
+          <t>跳跃</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>adolescents</t>
+          <t>legendary</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>青少年</t>
+          <t>名声大噪</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -12192,22 +12192,22 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>conclusive</t>
+          <t>self-portrait</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>确凿的</t>
+          <t>自拍照</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>attain</t>
+          <t>adolescents</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>取得</t>
+          <t>青少年</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -12894,22 +12894,22 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>begged to differ</t>
+          <t>devoid of</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>不敢苟同</t>
+          <t>完全没有</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>trivial</t>
+          <t>attain</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>微不足道的</t>
+          <t>取得</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -13596,22 +13596,22 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>viewers</t>
+          <t>conclusive</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>观众</t>
+          <t>确凿的</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>snack</t>
+          <t>trivial</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>零食</t>
+          <t>微不足道的</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -14298,22 +14298,22 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>damning</t>
+          <t>begged to differ</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>足以定罪的</t>
+          <t>不敢苟同</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>emblem</t>
+          <t>snack</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>象征</t>
+          <t>零食</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -15000,12 +15000,12 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Confronted with</t>
+          <t>viewers</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>面对</t>
+          <t>观众</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -15702,22 +15702,22 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>sheer</t>
+          <t>damning</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>完全的</t>
+          <t>足以定罪的</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>restraint</t>
+          <t>emblem</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>克制</t>
+          <t>象征</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -16404,22 +16404,22 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>disbelief</t>
+          <t>Confronted with</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>不相信</t>
+          <t>面对</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>glorified</t>
+          <t>restraint</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>美化</t>
+          <t>克制</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -17106,22 +17106,22 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>pondered</t>
+          <t>sheer</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>思考</t>
+          <t>完全</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>predictor</t>
+          <t>glorified</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>预测指标</t>
+          <t>美化</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -17808,12 +17808,12 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>disquieting</t>
+          <t>disbelief</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>令人不安的</t>
+          <t>不相信</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -18510,22 +18510,22 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>proposition</t>
+          <t>pondered</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>观点</t>
+          <t>仔细思考了</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>foundation</t>
+          <t>predictor</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>基础</t>
+          <t>预测指标</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -19212,22 +19212,22 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>incompetence</t>
+          <t>disquieting</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>无能</t>
+          <t>令人不安的</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>precarious</t>
+          <t>foundation</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>不稳固的</t>
+          <t>根据</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -19914,22 +19914,22 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>cloak</t>
+          <t>proposition</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>掩盖</t>
+          <t>观点</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>predominantly</t>
+          <t>precarious</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>主要地</t>
+          <t>并不牢靠</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -20616,22 +20616,22 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>robbing</t>
+          <t>incompetence</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>剥夺</t>
+          <t>无能</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>faculty</t>
+          <t>a few dozen</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>教职员工</t>
+          <t>几十个</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -21318,22 +21318,22 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>discernment</t>
+          <t>cloak</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>洞察力</t>
+          <t>掩藏住</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>postgraduate</t>
+          <t>predominantly</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>研究生的</t>
+          <t>主要</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -22020,22 +22020,22 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>deficiencies</t>
+          <t>robbing</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>缺陷</t>
+          <t>剥夺</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>homogeneous</t>
+          <t>faculty</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>同质的</t>
+          <t>教师</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -22722,22 +22722,22 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>quizzed</t>
+          <t>discernment</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>测验</t>
+          <t>识别能力</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>privileged</t>
+          <t>postgraduate</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>享有特权的</t>
+          <t>研究生</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -23424,22 +23424,22 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>undergraduates</t>
+          <t>deficiencies</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>本科生</t>
+          <t>不足</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>scarcely</t>
+          <t>homogeneous</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>几乎不</t>
+          <t>同质的</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -24126,22 +24126,22 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>logical</t>
+          <t>paper</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>逻辑的</t>
+          <t>论文</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>ordinary</t>
+          <t>privileged</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>普通的</t>
+          <t>优越的</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -24828,22 +24828,22 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>scorers</t>
+          <t>quizzed</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>得分者</t>
+          <t>测试了</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>prosperous</t>
+          <t>scarcely</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>富裕的</t>
+          <t>几乎不</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -25530,22 +25530,22 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>generously</t>
+          <t>undergraduates</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>大方地</t>
+          <t>本科生</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>foster</t>
+          <t>ordinary</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>培养</t>
+          <t>普通的</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -26232,22 +26232,22 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>achievers</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>成就高的人</t>
+          <t>逻辑</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>conceptual</t>
+          <t>prosperous</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>概念上的</t>
+          <t>富裕的</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -26934,22 +26934,22 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>undue</t>
+          <t>scorers</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>过分的</t>
+          <t>答题者</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>replication</t>
+          <t>foster</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>重复研究</t>
+          <t>既能培养</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -27636,22 +27636,22 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>modesty</t>
+          <t>generously</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>谦虚</t>
+          <t>大方地</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>modified</t>
+          <t>alike</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>修改过的</t>
+          <t>二者兼顾</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -28338,22 +28338,22 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>unskilled</t>
+          <t>achievers</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>能力不足者</t>
+          <t>成绩优异者</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>youngsters</t>
+          <t>conceptual</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>儿童</t>
+          <t>概念性的</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -29040,22 +29040,22 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>dual</t>
+          <t>undue</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>双重的</t>
+          <t>过分的</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>diverse</t>
+          <t>replication</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>多样的</t>
+          <t>重复实验</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -29742,22 +29742,22 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>appraisal</t>
+          <t>modesty</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>评估</t>
+          <t>谦虚</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>assessed</t>
+          <t>modified</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>评估</t>
+          <t>调整过的</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -30444,22 +30444,22 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>execution</t>
+          <t>unskilled</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>执行</t>
+          <t>能力不足的</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Adjusting for</t>
+          <t>diverse</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>控制</t>
+          <t>多种不同的</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -31146,22 +31146,22 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>Detractors</t>
+          <t>dual</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>批评者</t>
+          <t>双重</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>cognitive</t>
+          <t>youngsters</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>认知的</t>
+          <t>儿童或青少年</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -31848,22 +31848,22 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>disparity</t>
+          <t>appraisal</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>差距</t>
+          <t>评估</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>statistically</t>
+          <t>assessed</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>在统计上</t>
+          <t>评估</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -32550,22 +32550,22 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>mirage</t>
+          <t>calls for</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>假象</t>
+          <t>需要</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>insignificant</t>
+          <t>link</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>不显著的</t>
+          <t>关联性</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -33252,22 +33252,22 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>partially</t>
+          <t>execution</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>部分地</t>
+          <t>执行</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>worthless</t>
+          <t>Adjusting for</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>毫无价值的</t>
+          <t>调整</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
@@ -33954,22 +33954,22 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>tangible</t>
+          <t>Detractors</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>切实的</t>
+          <t>批评者</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>reflect</t>
+          <t>cognitive</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>反映</t>
+          <t>认知</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -34656,22 +34656,22 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>garnered</t>
+          <t>disparity</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>获得</t>
+          <t>差异</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>substantive</t>
+          <t>statistically</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>实质性的</t>
+          <t>统计上</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
@@ -35358,22 +35358,22 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>In fairness</t>
+          <t>mirage</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>平心而论</t>
+          <t>假象</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>context</t>
+          <t>insignificant</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>背景</t>
+          <t>微不足道</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -36060,22 +36060,22 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>empirically</t>
+          <t>partially</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>凭经验地</t>
+          <t>部分</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>betrayed</t>
+          <t>worthless</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>辜负</t>
+          <t>毫无价值</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
@@ -36762,22 +36762,22 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>staking … on</t>
+          <t>tangible</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>以…作赌注</t>
+          <t>切实存在的</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>markedly</t>
+          <t>reflect</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>明显地</t>
+          <t>反映</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
@@ -37244,22 +37244,22 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>liberty</t>
+          <t>garnered</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>自由</t>
+          <t>赢得了</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>peers</t>
+          <t>substantive</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>同龄人</t>
+          <t>实质性的</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
@@ -37624,14 +37624,24 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>In fairness</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>平心而论</t>
+        </is>
+      </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>perseveres</t>
+          <t>context</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>坚持</t>
+          <t>背景</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
@@ -37876,14 +37886,24 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>empirically</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>用实证的方法</t>
+        </is>
+      </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>trustworthy</t>
+          <t>betrayed</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>值得信赖的</t>
+          <t>辜负</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
@@ -38088,6 +38108,26 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>liberty</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>自由</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>markedly</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>明显</t>
+        </is>
+      </c>
       <c r="BC57" s="3" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -38106,6 +38146,64 @@
       <c r="DD57" s="4" t="inlineStr">
         <is>
           <t>相互关联的</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>staking</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>赌</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>peers</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>同龄人</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>perseveres</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>坚持</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>depends on</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>取决于</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>trustworthy</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>可信</t>
         </is>
       </c>
     </row>

--- a/视频/70篇重点词汇.xlsx
+++ b/视频/70篇重点词汇.xlsx
@@ -1682,12 +1682,12 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>brew</t>
+          <t>broth</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>调制饮料</t>
+          <t>清汤</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>broth</t>
+          <t>brew</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>肉汤</t>
+          <t>混合液</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>微生物的</t>
+          <t>微生物</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>刮</t>
+          <t>刮了下来</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>spicy</t>
+          <t>ulcers</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>辛辣的</t>
+          <t>溃疡</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -6596,12 +6596,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>acid</t>
+          <t>spicy</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>胃酸</t>
+          <t>辛辣的</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -7298,12 +7298,12 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>secretion</t>
+          <t>acid</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>分泌</t>
+          <t>胃酸</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -8000,12 +8000,12 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>bacterium</t>
+          <t>secretion</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>细菌</t>
+          <t>分泌</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -10106,12 +10106,12 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>withstand</t>
+          <t>bacterium</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>承受</t>
+          <t>细菌</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -10808,12 +10808,12 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>caustic</t>
+          <t>withstand</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>腐蚀性的</t>
+          <t>经受住</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -11510,12 +11510,12 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>hostile</t>
+          <t>caustic</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>恶劣的</t>
+          <t>具有腐蚀性</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -12212,12 +12212,12 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>habitat</t>
+          <t>hostile</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>生存环境</t>
+          <t>不利的</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -12914,12 +12914,12 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>coiled</t>
+          <t>habitat</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>卷曲的</t>
+          <t>栖息环境</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -13616,12 +13616,12 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>gastric</t>
+          <t>pathologist</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>胃的</t>
+          <t>病理学家</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>biopsies</t>
+          <t>gastric</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>活检</t>
+          <t>胃部的</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -15020,12 +15020,12 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>collaborate</t>
+          <t>biopsies</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>合作</t>
+          <t>活检样本</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -15722,12 +15722,12 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>germ</t>
+          <t>coiled</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>病菌</t>
+          <t>盘绕的</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -16424,12 +16424,12 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>invariably</t>
+          <t>collaborate</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>无一例外地</t>
+          <t>合作</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
@@ -17126,12 +17126,12 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>unsuccessful</t>
+          <t>culture</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>不成功的</t>
+          <t>培养</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -17828,12 +17828,12 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>undisturbed</t>
+          <t>germ</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>未被动过的</t>
+          <t>病菌</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -18530,12 +18530,12 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>ordinarily</t>
+          <t>Attempts</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>通常</t>
+          <t>尝试</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -19232,12 +19232,12 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>binned</t>
+          <t>invariably</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>扔掉</t>
+          <t>无一例外地</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -19934,12 +19934,12 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>blossomed</t>
+          <t>unsuccessful</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>大量繁殖</t>
+          <t>未能成功</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
@@ -20636,12 +20636,12 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>unimpressed</t>
+          <t>undisturbed</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>不以为然的</t>
+          <t>原封不动的</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -21338,12 +21338,12 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>assessors</t>
+          <t>incubator</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>评审员</t>
+          <t>培养箱</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
@@ -22040,12 +22040,12 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>relegated</t>
+          <t>ordinarily</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>贬入</t>
+          <t>通常</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -22742,12 +22742,12 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>submissions</t>
+          <t>binned</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>投稿</t>
+          <t>被扔掉</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
@@ -23444,12 +23444,12 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>swine</t>
+          <t>blossomed</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>猪</t>
+          <t>蓬勃生长</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -24146,12 +24146,12 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>likewise</t>
+          <t>unimpressed</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>同样</t>
+          <t>未被留下深刻印象的</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -24848,12 +24848,12 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>in vain</t>
+          <t>assessors</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>徒劳</t>
+          <t>评审员</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -25550,12 +25550,12 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>guinea pig</t>
+          <t>relegated</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>小白鼠</t>
+          <t>贬入</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
@@ -26252,12 +26252,12 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>vomiting</t>
+          <t>submissions</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>呕吐</t>
+          <t>投稿</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -26954,12 +26954,12 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>disagreeable</t>
+          <t>swine</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>难闻的</t>
+          <t>猪</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
@@ -27656,12 +27656,12 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>odour</t>
+          <t>Efforts</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>气味</t>
+          <t>努力</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -28358,12 +28358,12 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>weariness</t>
+          <t>likewise</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>疲倦</t>
+          <t>同样</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
@@ -29060,12 +29060,12 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>inflammation</t>
+          <t>in vain</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>炎症</t>
+          <t>徒劳无功</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -29762,12 +29762,12 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>mucous membrane</t>
+          <t>guinea pig</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>黏膜</t>
+          <t>小白鼠</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
@@ -30464,12 +30464,12 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>precursor</t>
+          <t>vomiting</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>前兆</t>
+          <t>呕吐</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -31166,12 +31166,12 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>albeit</t>
+          <t>disagreeable</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>尽管</t>
+          <t>难闻的</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
@@ -31868,12 +31868,12 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>directly</t>
+          <t>odour</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>直接地</t>
+          <t>气味</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -32570,12 +32570,12 @@
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Spurred on</t>
+          <t>weariness</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>激励</t>
+          <t>疲倦感</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
@@ -33272,12 +33272,12 @@
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>insistent</t>
+          <t>revealed</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>执意的</t>
+          <t>显示出</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
@@ -33974,12 +33974,12 @@
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>spouse</t>
+          <t>mucous membrane</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>配偶</t>
+          <t>黏膜</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
@@ -34676,12 +34676,12 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>antibiotics</t>
+          <t>inflammation</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>抗生素</t>
+          <t>炎症</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
@@ -35378,12 +35378,12 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>medication</t>
+          <t>precursor</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>药物</t>
+          <t>前兆</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
@@ -36080,12 +36080,12 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>willingly</t>
+          <t>albeit</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>自愿地</t>
+          <t>尽管</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
@@ -36780,6 +36780,16 @@
           <t>反映</t>
         </is>
       </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>directly</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
           <t>remodel</t>
@@ -37262,6 +37272,16 @@
           <t>实质性的</t>
         </is>
       </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>insistent</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>坚决的</t>
+        </is>
+      </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
           <t>intensive</t>
@@ -37644,6 +37664,16 @@
           <t>背景</t>
         </is>
       </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>spouse</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>妻子</t>
+        </is>
+      </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
           <t>occupied</t>
@@ -37906,6 +37936,16 @@
           <t>辜负</t>
         </is>
       </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>Spurred on</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>催促</t>
+        </is>
+      </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
           <t>claimed</t>
@@ -38128,6 +38168,16 @@
           <t>明显</t>
         </is>
       </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>antibiotics</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>抗生素</t>
+        </is>
+      </c>
       <c r="BC57" s="3" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -38170,6 +38220,16 @@
           <t>同龄人</t>
         </is>
       </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>medication</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>药物</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="C59" s="3" t="inlineStr">
@@ -38182,6 +38242,16 @@
           <t>坚持</t>
         </is>
       </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>作用</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="C60" s="3" t="inlineStr">
@@ -38192,6 +38262,16 @@
       <c r="D60" s="4" t="inlineStr">
         <is>
           <t>取决于</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>willingly</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>心甘情愿地</t>
         </is>
       </c>
     </row>

--- a/视频/70篇重点词汇.xlsx
+++ b/视频/70篇重点词汇.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EJ61"/>
+  <dimension ref="A1:EJ62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -24151,7 +24151,7 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>未被留下深刻印象的</t>
+          <t>不以为然的</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -24853,7 +24853,7 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>评审员</t>
+          <t>评审</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -33272,12 +33272,12 @@
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>revealed</t>
+          <t>set in</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>显示出</t>
+          <t>出现了</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
@@ -33974,12 +33974,12 @@
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>mucous membrane</t>
+          <t>revealed</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>黏膜</t>
+          <t>显示出</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
@@ -34676,12 +34676,12 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>inflammation</t>
+          <t>mucous membrane</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>炎症</t>
+          <t>黏膜</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
@@ -35378,12 +35378,12 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>precursor</t>
+          <t>inflammation</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>前兆</t>
+          <t>炎症</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
@@ -36080,12 +36080,12 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>albeit</t>
+          <t>precursor</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>尽管</t>
+          <t>前兆</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
@@ -36782,12 +36782,12 @@
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>directly</t>
+          <t>albeit</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>直接</t>
+          <t>尽管</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
@@ -37274,12 +37274,12 @@
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>insistent</t>
+          <t>directly</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>坚决的</t>
+          <t>直接</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
@@ -37666,12 +37666,12 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>spouse</t>
+          <t>insistent</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>妻子</t>
+          <t>坚决的</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
@@ -37938,12 +37938,12 @@
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Spurred on</t>
+          <t>spouse</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>催促</t>
+          <t>妻子</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
@@ -38170,12 +38170,12 @@
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>antibiotics</t>
+          <t>Spurred on</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>抗生素</t>
+          <t>催促</t>
         </is>
       </c>
       <c r="BC57" s="3" t="inlineStr">
@@ -38222,12 +38222,12 @@
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>medication</t>
+          <t>antibiotics</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>药物</t>
+          <t>抗生素</t>
         </is>
       </c>
     </row>
@@ -38244,12 +38244,12 @@
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>medication</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>作用</t>
+          <t>药物</t>
         </is>
       </c>
     </row>
@@ -38266,12 +38266,12 @@
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>willingly</t>
+          <t>role</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>心甘情愿地</t>
+          <t>作用</t>
         </is>
       </c>
     </row>
@@ -38284,6 +38284,28 @@
       <c r="D61" s="4" t="inlineStr">
         <is>
           <t>可信</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>willingly</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>心甘情愿地</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>prize citation</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>奖项颁奖词</t>
         </is>
       </c>
     </row>

--- a/视频/70篇重点词汇.xlsx
+++ b/视频/70篇重点词汇.xlsx
@@ -1697,7 +1697,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>一口气说出</t>
+          <t>脱口说出</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>来之不易的</t>
+          <t>来之不易</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -4505,7 +4505,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>有抱负的</t>
+          <t>有志向的</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -7313,7 +7313,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>应考者</t>
+          <t>考生们</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -8712,12 +8712,12 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>committing … to memory</t>
+          <t>labyrinth</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>把…记住</t>
+          <t>迷宫</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -9414,12 +9414,12 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>labyrinth</t>
+          <t>committing</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>迷宫</t>
+          <t>记</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
@@ -10121,7 +10121,7 @@
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>取得资格</t>
+          <t>合格</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -10823,7 +10823,7 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>扫描</t>
+          <t>扫描了</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
@@ -11520,12 +11520,12 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>vital</t>
+          <t>hippocampus</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>至关重要的</t>
+          <t>海马体</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -12924,12 +12924,12 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>vital</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>后部的</t>
+          <t>至关重要的</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -13626,12 +13626,12 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>portion</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>部分</t>
+          <t>后面的</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
@@ -14328,12 +14328,12 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>anterior</t>
+          <t>portion</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>前部的</t>
+          <t>部分</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
@@ -15030,12 +15030,12 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>anterior</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>不确定的</t>
+          <t>前面的</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
@@ -15732,12 +15732,12 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>innate</t>
+          <t>uncertain</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>天生的</t>
+          <t>不确定的</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -16434,12 +16434,12 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>flair</t>
+          <t>innate</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>天赋</t>
+          <t>天生的</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
@@ -17141,7 +17141,7 @@
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>空间的</t>
+          <t>空间</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -17838,12 +17838,12 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>lured</t>
+          <t>flair</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>吸引</t>
+          <t>天赋</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
@@ -18540,12 +18540,12 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>occupation</t>
+          <t>lured</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>职业</t>
+          <t>吸引</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
@@ -19242,12 +19242,12 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>stressful</t>
+          <t>occupation</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>压力大的</t>
+          <t>职业</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
@@ -19944,12 +19944,12 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>culprit</t>
+          <t>stressful</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>罪魁祸首</t>
+          <t>紧张的</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
@@ -20646,12 +20646,12 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>dispelled</t>
+          <t>culprit</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>消除</t>
+          <t>罪魁祸首</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
@@ -21348,12 +21348,12 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>notion</t>
+          <t>dispelled</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>观点</t>
+          <t>打消了</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
@@ -22050,12 +22050,12 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>dense with</t>
+          <t>notion</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>充满</t>
+          <t>想法</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
@@ -22752,12 +22752,12 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>nerve cells</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>神经细胞</t>
+          <t>密布</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
@@ -23454,12 +23454,12 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>confined</t>
+          <t>nerve</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>局限于</t>
+          <t>神经</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
@@ -24156,12 +24156,12 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>predetermined</t>
+          <t>confined</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>预先确定的</t>
+          <t>局限于</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
@@ -24858,12 +24858,12 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>equivalent</t>
+          <t>predetermined</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>相当的</t>
+          <t>预先确定的</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
@@ -25560,12 +25560,12 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>longitudinal</t>
+          <t>equivalent</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>纵向的</t>
+          <t>相当的</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
@@ -26262,12 +26262,12 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>tackled</t>
+          <t>longitudinal</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>处理</t>
+          <t>纵向的</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>trainees</t>
+          <t>tackled</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>学员</t>
+          <t>处理</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
@@ -27666,12 +27666,12 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>enrolment</t>
+          <t>trainees</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>入学</t>
+          <t>学员</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
@@ -28368,12 +28368,12 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>exhibited</t>
+          <t>enrolment</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>显示出</t>
+          <t>入学</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
@@ -29070,12 +29070,12 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>expansion</t>
+          <t>exhibited</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>扩大</t>
+          <t>表现出</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
@@ -29772,12 +29772,12 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>sequence</t>
+          <t>expansion</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>顺序</t>
+          <t>扩大</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
@@ -30474,12 +30474,12 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>preceded</t>
+          <t>sequence</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>先于</t>
+          <t>先后顺序</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
@@ -31176,12 +31176,12 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>enlargement</t>
+          <t>preceded</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>增大</t>
+          <t>先于</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
@@ -31878,12 +31878,12 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>entail</t>
+          <t>enlargement</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>涉及</t>
+          <t>增大</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
@@ -32580,12 +32580,12 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>trade-off</t>
+          <t>entail</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>权衡取舍</t>
+          <t>必然带来</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr">
@@ -33282,12 +33282,12 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>trailed</t>
+          <t>trade-off</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>落后于</t>
+          <t>代价</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
@@ -33984,12 +33984,12 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>intricate</t>
+          <t>trailed</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>复杂的</t>
+          <t>落后于</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
@@ -34686,12 +34686,12 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>cohorts</t>
+          <t>intricate</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>群体</t>
+          <t>复杂的</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
@@ -35388,12 +35388,12 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>exclusively</t>
+          <t>cohorts</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>全部</t>
+          <t>样本群体</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
@@ -36090,12 +36090,12 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>imply</t>
+          <t>exclusively</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>表明</t>
+          <t>专门</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
@@ -36792,12 +36792,12 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>remodel</t>
+          <t>imply</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>重塑</t>
+          <t>暗示/意味着</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr">
@@ -37284,12 +37284,12 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>intensive</t>
+          <t>remodel</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>高强度的</t>
+          <t>重塑</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
@@ -37676,12 +37676,12 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>occupied</t>
+          <t>intensive</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>占据</t>
+          <t>高强度的</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
@@ -37948,12 +37948,12 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>claimed</t>
+          <t>occupied</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>占用</t>
+          <t>占据了</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
@@ -38176,6 +38176,16 @@
       <c r="F57" s="4" t="inlineStr">
         <is>
           <t>催促</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>claimed</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>占用</t>
         </is>
       </c>
       <c r="BC57" s="3" t="inlineStr">

--- a/视频/70篇重点词汇.xlsx
+++ b/视频/70篇重点词汇.xlsx
@@ -28388,12 +28388,12 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>innocently</t>
+          <t>unwittingly</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t>无心地</t>
+          <t>不知情地</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">

--- a/视频/70篇重点词汇.xlsx
+++ b/视频/70篇重点词汇.xlsx
@@ -1717,7 +1717,7 @@
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>驯马师</t>
+          <t>驯兽师</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
@@ -5227,7 +5227,7 @@
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>才华</t>
+          <t>过人的才智</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
@@ -5924,12 +5924,12 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>demonstrations</t>
+          <t>courtyard</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>表演</t>
+          <t>庭院</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
@@ -6626,12 +6626,12 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>courtyard</t>
+          <t>demonstrations</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>庭院</t>
+          <t>演示/展示</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -7333,7 +7333,7 @@
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>聪明的</t>
+          <t>聪明</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
@@ -11540,12 +11540,12 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>zoological garden</t>
+          <t>zoological</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>动物园</t>
+          <t>动物</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
@@ -13651,7 +13651,7 @@
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>欺骗</t>
+          <t>骗局</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
@@ -14353,7 +14353,7 @@
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>证明</t>
+          <t>证实了</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
@@ -15055,7 +15055,7 @@
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>真实的</t>
+          <t>真实可信</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
@@ -19964,12 +19964,12 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>ignorant of</t>
+          <t>ignorant</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>不知道</t>
+          <t>一无所知的</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
@@ -21373,7 +21373,7 @@
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>看不见的</t>
+          <t>不可见</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
@@ -23474,12 +23474,12 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>lean forward</t>
+          <t>lean</t>
         </is>
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>前倾</t>
+          <t>倾身</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
@@ -24181,7 +24181,7 @@
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>紧张</t>
+          <t>紧张感</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
@@ -24883,7 +24883,7 @@
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
-          <t>挺直身子</t>
+          <t>挺直</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
@@ -25585,7 +25585,7 @@
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>猛抬</t>
+          <t>猛地一抬</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
@@ -26287,7 +26287,7 @@
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
-          <t>手势</t>
+          <t>姿势</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
@@ -28388,12 +28388,12 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>unwittingly</t>
+          <t>deceive</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t>不知情地</t>
+          <t>欺骗</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
@@ -29090,12 +29090,12 @@
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>deceive</t>
+          <t>unwittingly</t>
         </is>
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>欺骗</t>
+          <t>毫不知情地</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
@@ -29797,7 +29797,7 @@
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
-          <t>双盲的</t>
+          <t>双盲</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
@@ -31898,12 +31898,12 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>phenomenon</t>
+          <t>bias</t>
         </is>
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t>现象</t>
+          <t>偏差</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
@@ -32600,12 +32600,12 @@
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>bias</t>
+          <t>phenomenon</t>
         </is>
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
-          <t>偏差</t>
+          <t>现象</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
@@ -34009,7 +34009,7 @@
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
-          <t>行为的</t>
+          <t>行为</t>
         </is>
       </c>
       <c r="M49" s="3" t="inlineStr">
@@ -34706,12 +34706,12 @@
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>sensitive</t>
+          <t>attentive</t>
         </is>
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
-          <t>敏感的</t>
+          <t>专注的</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
@@ -35408,12 +35408,12 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>attentive</t>
+          <t>sensitive</t>
         </is>
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
-          <t>专注的</t>
+          <t>敏感</t>
         </is>
       </c>
       <c r="M51" s="3" t="inlineStr">
